--- a/mosip_master/xlsx/identity_schema.xlsx
+++ b/mosip_master/xlsx/identity_schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22A5529-1892-4310-9345-7DEEFA784792}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA486A0-4016-4BD7-9AA3-56B98C58C442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>lang_code</t>
   </si>
@@ -66,9 +66,6 @@
     <t>Mosip Sample identity</t>
   </si>
   <si>
-    <t>{"$schema":"http:\/\/json-schema.org\/draft-07\/schema#","description":"MOSIP Sample identity","additionalProperties":false,"title":"MOSIP identity","type":"object","definitions":{"simpleType":{"uniqueItems":true,"additionalItems":false,"type":"array","items":{"additionalProperties":false,"type":"object","required":["language","value"],"properties":{"language":{"type":"string"},"value":{"type":"string"}}}},"documentType":{"additionalProperties":false,"type":"object","properties":{"format":{"type":"string"},"type":{"type":"string"},"value":{"type":"string"},"refNumber":{"type":["string","null"]}}},"biometricsType":{"additionalProperties":false,"type":"object","properties":{"format":{"type":"string"},"version":{"type":"number","minimum":0},"value":{"type":"string"}}}},"properties":{"identity":{"additionalProperties":false,"type":"object","required":["IDSchemaVersion","fullName","dateOfBirth","gender","addressLine1","addressLine2","addressLine3","region","province","city","zone","postalCode","phone","email","proofOfIdentity","individualBiometrics"],"properties":{"proofOfAddress":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"gender":{"bioAttributes":[],"fieldCategory":"pvt","format":"","fieldType":"default","$ref":"#\/definitions\/simpleType"},"city":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"postalCode":{"bioAttributes":[],"validators":[{"validator":"^[(?i)A-Z0-9]{5}$|^NA$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"proofOfException-1":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"referenceIdentityNumber":{"bioAttributes":[],"validators":[{"validator":"^([0-9]{10,30})$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"kyc","type":"string","fieldType":"default"},"individualBiometrics":{"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/biometricsType"},"province":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"zone":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"proofOfDateOfBirth":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"addressLine1":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"addressLine2":{"bioAttributes":[],"validators":[{"validator":"^(?=.{3,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"residenceStatus":{"bioAttributes":[],"fieldCategory":"kyc","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"addressLine3":{"bioAttributes":[],"validators":[{"validator":"^(?=.{3,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"email":{"bioAttributes":[],"validators":[{"validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"introducerRID":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","type":"string","fieldType":"default"},"introducerBiometrics":{"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/biometricsType"},"fullName":{"bioAttributes":[],"validators":[{"validator":"^(?=.{3,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"dateOfBirth":{"bioAttributes":[],"validators":[{"validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])\/([0][1-9]|1[0-2])\/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"individualAuthBiometrics":{"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/biometricsType"},"introducerUIN":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","type":"string","fieldType":"default"},"proofOfIdentity":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"IDSchemaVersion":{"bioAttributes":[],"fieldCategory":"none","format":"none","type":"number","fieldType":"default","minimum":0},"proofOfException":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"phone":{"bioAttributes":[],"validators":[{"validator":"^[+]*([0-9]{1})([0-9]{9})$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"introducerName":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"proofOfRelationship":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"UIN":{"bioAttributes":[],"fieldCategory":"none","format":"none","type":"string","fieldType":"default"},"region":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"}}}}}</t>
-  </si>
-  <si>
     <t>PUBLISHED</t>
   </si>
   <si>
@@ -81,16 +78,451 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>Mosip Identity CRVS</t>
-  </si>
-  <si>
-    <t>CRVS sample identity</t>
-  </si>
-  <si>
-    <t>{"$schema":"http:\/\/json-schema.org\/draft-07\/schema#","description":"MOSIP Sample identity","additionalProperties":false,"title":"MOSIP identity","type":"object","definitions":{"simpleType":{"uniqueItems":true,"additionalItems":false,"type":"array","items":{"additionalProperties":false,"type":"object","required":["language","value"],"properties":{"language":{"type":"string"},"value":{"type":"string"}}}},"documentType":{"additionalProperties":false,"type":"object","properties":{"format":{"type":"string"},"type":{"type":"string"},"value":{"type":"string"},"refNumber":{"type":["string","null"]}}},"biometricsType":{"additionalProperties":false,"type":"object","properties":{"format":{"type":"string"},"version":{"type":"number","minimum":0},"value":{"type":"string"}}}},"properties":{"identity":{"additionalProperties":false,"type":"object","required":["IDSchemaVersion","fullName","dateOfBirth","gender","addressLine1","addressLine2","addressLine3","region","province","city","zone","postalCode","phone","email","proofOfIdentity","individualBiometrics"],"properties":{"proofOfAddress":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"gender":{"bioAttributes":[],"fieldCategory":"pvt","format":"","fieldType":"default","$ref":"#\/definitions\/simpleType"},"city":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"postalCode":{"bioAttributes":[],"validators":[{"validator":"^[(?i)A-Z0-9]{5}$|^NA$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"proofOfException-1":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"referenceIdentityNumber":{"bioAttributes":[],"validators":[{"validator":"^([0-9]{10,30})$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"kyc","type":"string","fieldType":"default"},"individualBiometrics":{"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/biometricsType"},"province":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"zone":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"proofOfDateOfBirth":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"addressLine1":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"addressLine2":{"bioAttributes":[],"validators":[{"validator":"^(?=.{3,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"residenceStatus":{"bioAttributes":[],"fieldCategory":"kyc","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"addressLine3":{"bioAttributes":[],"validators":[{"validator":"^(?=.{3,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"email":{"bioAttributes":[],"validators":[{"validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"introducerRID":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","type":"string","fieldType":"default"},"introducerBiometrics":{"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/biometricsType"},"fullName":{"bioAttributes":[],"validators":[{"validator":"^(?=.{3,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"dateOfBirth":{"bioAttributes":[],"validators":[{"validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])\/([0][1-9]|1[0-2])\/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"individualAuthBiometrics":{"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/biometricsType"},"introducerUIN":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","type":"string","fieldType":"default"},"proofOfIdentity":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"IDSchemaVersion":{"bioAttributes":[],"fieldCategory":"none","format":"none","type":"number","fieldType":"default","minimum":0},"proofOfException":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"phone":{"bioAttributes":[],"validators":[{"validator":"^[+]*([0-9]{1})([0-9]{9})$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"introducerName":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"proofOfRelationship":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/documentType"},"UIN":{"bioAttributes":[],"fieldCategory":"none","format":"none","type":"string","fieldType":"default"},"region":{"bioAttributes":[],"validators":[{"validator":"^(?=.{0,50}$).*","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","fieldType":"default","$ref":"#\/definitions\/simpleType"},"introducerInfoToken":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","type":"string","fieldType":"default"},"deceasedInformer":{"bioAttributes":[],"fieldCategory":"evidence","format":"none","type":"string","fieldType":"default"},"deceasedDeclarationDate":{"bioAttributes":[],"validators":[{"validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"declaredAsDeceased":{"bioAttributes":[],"validators":[{"validator":"^(Y|N)$","arguments":[],"type":"regex"}],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"},"typeOfDeath":{"bioAttributes":[],"fieldCategory":"pvt","format":"none","type":"string","fieldType":"default"}}}}}</t>
+    <t>{
+	"$schema": "http:\/\/json-schema.org\/draft-07\/schema#",
+	"description": "MOSIP Sample identity",
+	"additionalProperties": false,
+	"title": "MOSIP identity",
+	"type": "object",
+	"definitions": {
+		"simpleType": {
+			"uniqueItems": true,
+			"additionalItems": false,
+			"type": "array",
+			"items": {
+				"additionalProperties": false,
+				"type": "object",
+				"required": [
+					"language",
+					"value"
+				],
+				"properties": {
+					"language": {
+						"type": "string"
+					},
+					"value": {
+						"type": "string"
+					}
+				}
+			}
+		},
+		"documentType": {
+			"additionalProperties": false,
+			"type": "object",
+			"properties": {
+				"format": {
+					"type": "string"
+				},
+				"type": {
+					"type": "string"
+				},
+				"value": {
+					"type": "string"
+				},
+				"refNumber": {
+					"type": [
+						"string",
+						"null"
+					]
+				}
+			}
+		},
+		"biometricsType": {
+			"additionalProperties": false,
+			"type": "object",
+			"properties": {
+				"format": {
+					"type": "string"
+				},
+				"version": {
+					"type": "number",
+					"minimum": 0
+				},
+				"value": {
+					"type": "string"
+				}
+			}
+		}
+	},
+	"properties": {
+		"identity": {
+			"additionalProperties": false,
+			"type": "object",
+			"required": [
+				"IDSchemaVersion",
+				"fullName",
+				"dateOfBirth",
+				"gender",
+				"addressLine1",
+				"addressLine2",
+				"addressLine3",
+				"region",
+				"province",
+				"city",
+				"zone",
+				"postalCode",
+				"phone",
+				"email",
+				"proofOfIdentity",
+				"individualBiometrics"
+			],
+			"properties": {
+				"proofOfAddress": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/documentType"
+				},
+				"gender": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"city": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(?=.{0,50}$).*",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"postalCode": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^[(?i)A-Z0-9]{5}$|^NA$",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"proofOfException-1": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "evidence",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/documentType"
+				},
+				"referenceIdentityNumber": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^([0-9]{10,30})$",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "kyc",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"individualBiometrics": {
+					"bioAttributes": [
+						"leftEye",
+						"rightEye",
+						"rightIndex",
+						"rightLittle",
+						"rightRing",
+						"rightMiddle",
+						"leftIndex",
+						"leftLittle",
+						"leftRing",
+						"leftMiddle",
+						"leftThumb",
+						"rightThumb",
+						"face"
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/biometricsType"
+				},
+				"province": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(?=.{0,50}$).*",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"zone": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"proofOfDateOfBirth": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/documentType"
+				},
+				"addressLine1": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(?=.{0,50}$).*",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"addressLine2": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(?=.{3,50}$).*",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"residenceStatus": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "kyc",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"addressLine3": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(?=.{3,50}$).*",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"email": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"introducerRID": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "evidence",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"introducerBiometrics": {
+					"bioAttributes": [
+						"leftEye",
+						"rightEye",
+						"rightIndex",
+						"rightLittle",
+						"rightRing",
+						"rightMiddle",
+						"leftIndex",
+						"leftLittle",
+						"leftRing",
+						"leftMiddle",
+						"leftThumb",
+						"rightThumb",
+						"face"
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/biometricsType"
+				},
+				"fullName": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(?=.{3,50}$).*",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"dateOfBirth": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])\/([0][1-9]|1[0-2])\/([0][1-9]|[1-2][0-9]|3[01])$",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"individualAuthBiometrics": {
+					"bioAttributes": [
+						"leftEye",
+						"rightEye",
+						"rightIndex",
+						"rightLittle",
+						"rightRing",
+						"rightMiddle",
+						"leftIndex",
+						"leftLittle",
+						"leftRing",
+						"leftMiddle",
+						"leftThumb",
+						"rightThumb",
+						"face"
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/biometricsType"
+				},
+				"introducerUIN": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "evidence",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"proofOfIdentity": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/documentType"
+				},
+				"IDSchemaVersion": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "none",
+					"format": "none",
+					"type": "number",
+					"fieldType": "default",
+					"minimum": 0
+				},
+				"proofOfException": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "evidence",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/documentType"
+				},
+				"phone": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^[+]*([0-9]{1})([0-9]{9})$",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"introducerName": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "evidence",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"proofOfRelationship": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/documentType"
+				},
+				"UIN": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "none",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"preferredLang": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "dynamic"
+				},
+				"region": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(?=.{0,50}$).*",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				}
+			}
+		}
+	}
+}</t>
   </si>
 </sst>
 </file>
@@ -147,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -160,9 +592,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -481,24 +910,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ3"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AMJ2"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="1"/>
-    <col min="2" max="2" width="8.44140625" style="2"/>
-    <col min="3" max="3" width="11.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="75.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" style="1"/>
+    <col min="2" max="2" width="8.453125" style="2"/>
+    <col min="3" max="3" width="11.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" style="1"/>
+    <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" style="2" customWidth="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.44140625" style="2"/>
-    <col min="11" max="1023" width="8.44140625" style="1"/>
-    <col min="1024" max="1024" width="11.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="2"/>
+    <col min="11" max="1023" width="8.453125" style="1"/>
+    <col min="1024" max="1024" width="11.54296875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -530,68 +959,36 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2">
         <v>1001</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="1">
         <v>0.1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
